--- a/public/sap-reporting/expansion-150-downloads/EXT-PP15-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP15-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rbd13cb3f38c441f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R452dd4e095a84f58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R19bf7a7486e74f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R1b8baca22b034d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R6d490a3459e4485f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Ra3a7046af9cc47b0"/>
   </x:sheets>
 </x:workbook>
 </file>
